--- a/Result/profitability/2520.xlsx
+++ b/Result/profitability/2520.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,16 +669,16 @@
         <v>0.45</v>
       </c>
       <c r="M2" t="n">
-        <v>1.02</v>
+        <v>0.8749999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>25.32375</v>
+        <v>24.42</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.38</v>
       </c>
       <c r="M3" t="n">
-        <v>0.7537499999999999</v>
+        <v>0.6787499999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>23.87125</v>
+        <v>23.4525</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.26</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5424999999999999</v>
+        <v>0.61</v>
       </c>
       <c r="N4" t="n">
-        <v>22.8775</v>
+        <v>23.235</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.28</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4062499999999999</v>
+        <v>0.5175</v>
       </c>
       <c r="N5" t="n">
-        <v>20.86875</v>
+        <v>21.51125</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.6</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4237499999999998</v>
+        <v>0.5212499999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>20.9275</v>
+        <v>21.9575</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.33</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3937499999999999</v>
+        <v>0.4512499999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>20.44625</v>
+        <v>21.02625</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>0.4087499999999999</v>
+        <v>0.5125</v>
       </c>
       <c r="N8" t="n">
-        <v>20.96375</v>
+        <v>21.505</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1403,16 +1403,16 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2520</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>8363</v>
+      </c>
+      <c r="D75" t="n">
+        <v>6037</v>
+      </c>
+      <c r="E75" t="n">
+        <v>2326</v>
+      </c>
+      <c r="F75" t="n">
+        <v>27.81</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1755</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>20.98%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>65</v>
+      </c>
+      <c r="J75" t="n">
+        <v>1819</v>
+      </c>
+      <c r="K75" t="n">
+        <v>801</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.1325</v>
+      </c>
+      <c r="N75" t="n">
+        <v>25.98125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>1.596153846153846</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>4.329999999999998</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.184412265758092</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.8900000000000001</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>1.934782608695652</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>5.139999999999997</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.2267313630348478</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
